--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="240">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-12T14:26:59+00:00</t>
+    <t>2023-09-13T08:02:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -510,228 +510,242 @@
     <t>Bundle.entry.resource</t>
   </si>
   <si>
+    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/dui-documentreference}
+</t>
+  </si>
+  <si>
+    <t>A reference to a document</t>
+  </si>
+  <si>
+    <t>A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
+  </si>
+  <si>
+    <t>Usually, this is used for documents other than those defined by FHIR.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+  </si>
+  <si>
+    <t>Document[classCode="DOC" and moodCode="EVN"]</t>
+  </si>
+  <si>
+    <t>when describing a CDA</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search</t>
+  </si>
+  <si>
+    <t>Search related information</t>
+  </si>
+  <si>
+    <t>Information about the search process that lead to the creation of this entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-2</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.mode</t>
+  </si>
+  <si>
+    <t>match | include | outcome - why this is in the result set</t>
+  </si>
+  <si>
+    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
+  </si>
+  <si>
+    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Search ranking (between 0 and 1)</t>
+  </si>
+  <si>
+    <t>When searching, the server's search ranking score for the entry.</t>
+  </si>
+  <si>
+    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
+See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request</t>
+  </si>
+  <si>
+    <t>Additional execution information (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-3</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.method</t>
+  </si>
+  <si>
+    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+  </si>
+  <si>
+    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.url</t>
+  </si>
+  <si>
+    <t>URL for HTTP equivalent of this entry</t>
+  </si>
+  <si>
+    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
+  </si>
+  <si>
+    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>For managing cache currency</t>
+  </si>
+  <si>
+    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifMatch</t>
+  </si>
+  <si>
+    <t>For managing update contention</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>For conditional creates</t>
+  </si>
+  <si>
+    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response</t>
+  </si>
+  <si>
+    <t>Results of execution (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-4</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.status</t>
+  </si>
+  <si>
+    <t>Status response code (text optional)</t>
+  </si>
+  <si>
+    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.location</t>
+  </si>
+  <si>
+    <t>The location (if the operation returns a location)</t>
+  </si>
+  <si>
+    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.etag</t>
+  </si>
+  <si>
+    <t>The Etag for the resource (if relevant)</t>
+  </si>
+  <si>
+    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
+  </si>
+  <si>
+    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.lastModified</t>
+  </si>
+  <si>
+    <t>Server's date time modified</t>
+  </si>
+  <si>
+    <t>The date/time that the resource was modified on the server.</t>
+  </si>
+  <si>
+    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.outcome</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resource
 </t>
   </si>
   <si>
-    <t>A resource in the bundle</t>
-  </si>
-  <si>
-    <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search</t>
-  </si>
-  <si>
-    <t>Search related information</t>
-  </si>
-  <si>
-    <t>Information about the search process that lead to the creation of this entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-2</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.mode</t>
-  </si>
-  <si>
-    <t>match | include | outcome - why this is in the result set</t>
-  </si>
-  <si>
-    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
-  </si>
-  <si>
-    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Search ranking (between 0 and 1)</t>
-  </si>
-  <si>
-    <t>When searching, the server's search ranking score for the entry.</t>
-  </si>
-  <si>
-    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
-See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request</t>
-  </si>
-  <si>
-    <t>Additional execution information (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-3</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.method</t>
-  </si>
-  <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
-  </si>
-  <si>
-    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
-  </si>
-  <si>
-    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.url</t>
-  </si>
-  <si>
-    <t>URL for HTTP equivalent of this entry</t>
-  </si>
-  <si>
-    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
-  </si>
-  <si>
-    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>For managing cache currency</t>
-  </si>
-  <si>
-    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifMatch</t>
-  </si>
-  <si>
-    <t>For managing update contention</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>For conditional creates</t>
-  </si>
-  <si>
-    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response</t>
-  </si>
-  <si>
-    <t>Results of execution (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-4</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.status</t>
-  </si>
-  <si>
-    <t>Status response code (text optional)</t>
-  </si>
-  <si>
-    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.location</t>
-  </si>
-  <si>
-    <t>The location (if the operation returns a location)</t>
-  </si>
-  <si>
-    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.etag</t>
-  </si>
-  <si>
-    <t>The Etag for the resource (if relevant)</t>
-  </si>
-  <si>
-    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
-  </si>
-  <si>
-    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.lastModified</t>
-  </si>
-  <si>
-    <t>Server's date time modified</t>
-  </si>
-  <si>
-    <t>The date/time that the resource was modified on the server.</t>
-  </si>
-  <si>
-    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.outcome</t>
-  </si>
-  <si>
     <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
   </si>
   <si>
@@ -740,6 +754,9 @@
   <si>
     <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
 This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
+  </si>
+  <si>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1061,7 +1078,7 @@
     <col min="8" max="8" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="101.4140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3504,7 +3521,7 @@
         <v>34</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>154</v>
@@ -3515,7 +3532,9 @@
       <c r="M22" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="N22" s="2"/>
+      <c r="N22" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>34</v>
@@ -3576,16 +3595,16 @@
         <v>34</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>34</v>
@@ -3593,10 +3612,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3622,10 +3641,10 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3676,7 +3695,7 @@
         <v>34</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>35</v>
@@ -3685,7 +3704,7 @@
         <v>44</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>57</v>
@@ -3705,10 +3724,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3817,10 +3836,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3931,10 +3950,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4047,10 +4066,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4076,13 +4095,13 @@
         <v>66</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4111,10 +4130,10 @@
         <v>87</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>34</v>
@@ -4132,7 +4151,7 @@
         <v>34</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>35</v>
@@ -4161,10 +4180,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4187,16 +4206,16 @@
         <v>45</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4246,7 +4265,7 @@
         <v>34</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>35</v>
@@ -4275,10 +4294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4304,10 +4323,10 @@
         <v>105</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4358,7 +4377,7 @@
         <v>34</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>35</v>
@@ -4367,7 +4386,7 @@
         <v>44</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>57</v>
@@ -4387,10 +4406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4499,10 +4518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4613,10 +4632,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4729,10 +4748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4758,10 +4777,10 @@
         <v>66</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>134</v>
@@ -4793,28 +4812,28 @@
         <v>87</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>44</v>
@@ -4843,10 +4862,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4872,13 +4891,13 @@
         <v>59</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4928,7 +4947,7 @@
         <v>34</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>44</v>
@@ -4957,10 +4976,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4986,10 +5005,10 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>134</v>
@@ -5042,7 +5061,7 @@
         <v>34</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>35</v>
@@ -5071,10 +5090,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5100,13 +5119,13 @@
         <v>92</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5156,7 +5175,7 @@
         <v>34</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>35</v>
@@ -5185,10 +5204,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5214,10 +5233,10 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>134</v>
@@ -5270,7 +5289,7 @@
         <v>34</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>35</v>
@@ -5299,10 +5318,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5328,10 +5347,10 @@
         <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>134</v>
@@ -5384,7 +5403,7 @@
         <v>34</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>35</v>
@@ -5413,10 +5432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5442,10 +5461,10 @@
         <v>105</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5496,7 +5515,7 @@
         <v>34</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>35</v>
@@ -5505,7 +5524,7 @@
         <v>44</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>57</v>
@@ -5525,10 +5544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5637,10 +5656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5751,10 +5770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5867,10 +5886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5896,10 +5915,10 @@
         <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>134</v>
@@ -5952,7 +5971,7 @@
         <v>34</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>44</v>
@@ -5981,10 +6000,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6010,10 +6029,10 @@
         <v>59</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>138</v>
@@ -6066,7 +6085,7 @@
         <v>34</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>35</v>
@@ -6095,10 +6114,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6124,13 +6143,13 @@
         <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6180,7 +6199,7 @@
         <v>34</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>35</v>
@@ -6209,10 +6228,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6238,13 +6257,13 @@
         <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6294,7 +6313,7 @@
         <v>34</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>35</v>
@@ -6323,10 +6342,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6349,16 +6368,16 @@
         <v>45</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6408,7 +6427,7 @@
         <v>34</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>35</v>
@@ -6426,7 +6445,7 @@
         <v>34</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>34</v>
@@ -6437,10 +6456,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6463,19 +6482,19 @@
         <v>45</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>34</v>
@@ -6524,7 +6543,7 @@
         <v>34</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>35</v>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T08:02:35+00:00</t>
+    <t>2023-09-13T10:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T10:23:45+00:00</t>
+    <t>2023-09-13T10:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T10:41:32+00:00</t>
+    <t>2023-09-13T13:19:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T13:19:45+00:00</t>
+    <t>2023-09-13T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T14:55:53+00:00</t>
+    <t>2023-09-14T12:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-14T12:40:46+00:00</t>
+    <t>2023-09-14T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-14T13:51:30+00:00</t>
+    <t>2023-09-15T08:58:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-15T08:58:52+00:00</t>
+    <t>2023-09-18T08:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T14:13:30+00:00</t>
+    <t>2023-09-18T16:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T16:20:24+00:00</t>
+    <t>2023-09-20T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T09:28:33+00:00</t>
+    <t>2023-09-20T10:55:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
